--- a/mainWidget/mainWidget/src/database/计算模型-预热工艺模型.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-预热工艺模型.xlsx
@@ -26,7 +26,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>340.36210967-1067.26983815*A+224.43952784*B-232.50668176*C+531.22537911*D+301.92996804*E-272.00468157*F+7246.20722434*A^2+298.76335298*A*B-916.76663788*A*C+1973.63586011*A*D+1965.32179943*A*E-552.33403266*A*F-267.12344202*B^2-83.25807155*B*C+118.32458792*B*D+196.94548638*B*E-23.78257687*B*F+598.49323067*C^2+149.35934868*C*D+34.71164314*C*E-252.25568167*C*F-497.47957785*D^2-49.07147517*D*E+129.61034877*D*F+327.83915059*E^2-336.65496753*E*F+808.76372735*F^2-12467.09212988*A^3-1506.22894326*A^2*B+2398.90470582*A^2*C-4050.30706421*A^2*D-4272.9119075*A^2*E+2198.12371809*A^2*F+350.96884875*A*B^2-99.08713132*A*B*C-46.68990051*A*B*D+260.68170225*A*B*E+140.0321197*A*B*F+364.59776476*A*C^2+795.25207065*A*C*D+791.09504031*A*C*E-467.73287573*A*C*F-730.80266957*A*D^2+906.01655557*A*D*E+977.46837326*A*D*F-253.26862744*A*E^2-811.18771601*A*E*F+435.14463685*A*F^2+152.04262591*B^3+4.30446398*B^2*C+235.99703487*B^2*D+197.63083881*B^2*E-201.5628914*B^2*F+113.81757717*B*C^2-38.57662377*B*C*D+0.73382546*B*C*E-109.63020617*B*C*F+109.61540992*B*D^2-131.29941918*B*D*E-8.83887643*B*D*F-67.95668944*B*E^2-145.33723259*B*E*F+460.49174563*B*F^2-1063.19187773*C^3+432.05296011*C^2*D+374.72910735*C^2*E+231.24544494*C^2*F-306.86645936*C*D^2-82.66240803*C*D*E+6.67850394*C*D*F+105.79290485*C*E^2-226.45415421*C*E*F+346.25519323*C*F^2+409.77875293*D^3+815.76930212*D^2*E-316.74095932*D^2*F+913.92252725*D*E^2-268.34571336*D*E*F+537.18820845*D*F^2-825.19274616*E^3-87.01156629*E^2*F+925.77834354*E*F^2-1654.97776971*F^3+5778.55726496*A^4+1583.65725439*A^3*B+16.98361215*A^3*C+5191.14300679*A^3*D+3990.74702*A^3*E-489.14965595*A^3*F-227.08094084*A^2*B^2-92.00773478*A^2*B*C+1540.89627581*A^2*B*D+1175.16177334*A^2*B*E-1465.60441867*A^2*B*F+173.21292235*A^2*C^2-2637.25298528*A^2*C*D-2748.55540693*A^2*C*E+486.96240587*A^2*C*F+377.95584225*A^2*D^2+3586.50993492*A^2*D*E-2737.64347914*A^2*D*F+276.69822499*A^2*E^2+238.59093033*A^2*E*F+92.3337951*A^2*F^2-68.73198138*A*B^3-0.15285679*A*B^2*C-68.1918589*A*B^2*D-132.72855045*A*B^2*E+170.80964598*A*B^2*F+177.85395147*A*B*C^2-147.57935416*A*B*C*D+6.10644722*A*B*C*E-54.21834406*A*B*C*F+799.04824506*A*B*D^2-632.83480424*A*B*D*E-28.01972865*A*B*D*F+789.28506093*A*B*E^2-766.58345674*A*B*E*F+425.67188644*A*B*F^2-841.43343567*A*C^3+809.11657718*A*C^2*D+807.03806201*A*C^2*E+177.62410398*A*C^2*F-461.18426449*A*C*D^2+357.22534809*A*C*D*E+392.95125693*A*C*D*F-222.41724342*A*C*E^2-501.3767877*A*C*E*F+121.78938872*A*C*F^2+246.48214214*A*D^3+164.791241*A*D^2*E-370.07611318*A*D^2*F-216.3706959*A*D*E^2-443.91603008*A*D*E*F+844.39001322*A*D*F^2-214.14506006*A*E^3+107.05927044*A*E^2*F+1043.54097404*A*E*F^2-1004.69159601*A*F^3+5.19197962*B^4-30.61731571*B^3*C-180.16141412*B^3*D-163.56709028*B^3*E+42.02072776*B^3*F-115.74992669*B^2*C^2+186.93160993*B^2*C*D+167.7485119*B^2*C*E-31.84835321*B^2*C*F-153.1351102*B^2*D^2+167.18251016*B^2*D*E+83.99793224*B^2*D*F-32.44276562*B^2*E^2-23.08956848*B^2*E*F+135.41007133*B^2*F^2-63.89131034*B*C^3+58.43499459*B*C^2*D+78.0902192*B*C^2*E+22.90820339*B*C^2*F+5.93824609*B*C*D^2-114.51916846*B*C*D*E-53.28889708*B*C*D*F-82.84780359*B*C*E^2-121.53807516*B*C*E*F+181.37641395*B*C*F^2-84.23618376*B*D^3+570.50243509*B*D^2*E+20.80711976*B*D^2*F+276.14616487*B*D*E^2-187.55469748*B*D*E*F+231.77207882*B*D*F^2+39.6731336*B*E^3-159.44391551*B*E^2*F+474.38429736*B*E*F^2-799.43394388*B*F^3+841.18524636*C^4-465.19276648*C^3*D-493.85469286*C^3*E-565.59652406*C^3*F+25.25341321*C^2*D^2+137.35543887*C^2*D*E+182.02589486*C^2*D*F+231.58309532*C^2*E^2+65.45956578*C^2*E*F+351.8142395*C^2*F^2+175.82604124*C*D^3+378.82131584*C*D^2*E-187.43381488*C*D^2*F+427.89792841*C*D*E^2-163.2361919*C*D*E*F+239.53076901*C*D*F^2-441.6597083*C*E^3-72.56911837*C*E^2*F+433.82583655*C*E*F^2-856.55222008*C*F^3-92.77090641*D^4-584.93085751*D^3*E+170.88879127*D^3*F-176.59980586*D^2*E^2+285.97966317*D^2*E*F+77.82103737*D^2*F^2-778.55977016*D*E^3+331.49569283*D*E^2*F+412.88005697*D*E*F^2-761.08571247*D*F^3+716.84265006*E^4-56.09643789*E^3*F+73.74173358*E^2*F^2-1052.59064854*E*F^3+1562.70740119*F^4</t>
+    <t>398.16005823+794.27983673*A-450.49134977*B+3008.53326895*C+5513.00965117*D-6751.73539640*E+1347.48946639*F-598.42604862*G+5141.88361939*A^2+976.46374519*A*B-356.92567264*A*C+4806.30419913*A*D+3059.57969242*A*E-564.93234819*A*F-7748.89036453*A*G-659.20504830*B^2-917.55416745*B*C+391.10092341*B*D+6080.86731302*B*E-1356.89235547*B*F-382.83622538*B*G-3954.69336810*C^2-14056.95261474*C*D+11026.73345929*C*E-652.07908397*C*F+85.69896657*C*G-501.19563225*D^2+4222.26049821*D*E-3487.76840439*D*F-2538.79224303*D*G+2888.91492280*E^2+2528.12767908*E*F-1831.34358607*E*G-172.79261182*F^2+267.99583898*F*G+2527.30472795*G^2+4254.44753680*A^3+1230.17495856*A^2*B+106.05852594*A^2*C+4014.07354562*A^2*D+3118.32008134*A^2*E-192.99854387*A^2*F-12304.39640200*A^2*G+2.08635973*A*B^2-94.20378305*A*B*C+1869.82904388*A*B*D+1426.55875547*A*B*E-8.15308995*A*B*F-2577.91963193*A*B*G+267.90440233*A*C^2-345.51822243*A*C*D+1097.84188248*A*C*E+341.11097198*A*C*F-369.76046430*A*C*G+92.79475483*A*D^2+4080.82187332*A*D*E-117.05239895*A*D*F-7529.42337444*A*D*G-79.69104296*A*E^2-270.02282330*A*E*F-6060.81910569*A*E*G+235.27647517*A*F^2+428.46087984*A*F*G+11422.08015297*A*G^2-63.07626247*B^3+5.20875147*B^2*C+15.42447229*B^2*D-9.26085896*B^2*E+1864.31206274*B^2*F-212.08392976*B^2*G+85.75667399*B*C^2+1910.68167501*B*C*D-3302.64371123*B*C*E+3025.24900275*B*C*F-27.54503235*B*C*G+543.47936874*B*D^2-3408.69102215*B*D*E+3009.12689223*B*D*F-1390.78453517*B*D*G+404.39043044*B*E^2-4106.37503469*B*E*F-861.06250584*B*E*G-2249.91340524*B*F^2+195.68229304*B*F*G+1161.68941675*B*G^2-592.28147378*C^3+10819.31955358*C^2*D+2024.25889641*C^2*E-2862.02521512*C^2*F-124.45113054*C^2*G+1041.05556340*C*D^2-1199.08050664*C*D*E+1110.55811201*C*D*F+216.10315616*C*D*G-5856.51606980*C*E^2-5274.28085525*C*E*F-523.17842216*C*E*G+4154.02319340*C*F^2-61.24213008*C*F*G+140.14709003*C*G^2+179.82738945*D^3+448.03842914*D^2*E-1238.00773247*D^2*F-140.73341181*D^2*G-17.45431677*D*E^2+2455.31439888*D*E*F-2880.59564339*D*E*G+556.35087046*D*F^2-89.99559867*D*F*G+3123.79874317*D*G^2-123.05905364*E^3+45.83672447*E^2*F+2.60468546*E^2*G+577.31603522*E*F^2+199.38889263*E*F*G+2535.33157748*E*G^2-764.87554144*F^3-40.02149206*F^2*G-451.02317205*F*G^2-3077.64268641*G^3</t>
   </si>
 </sst>
 </file>
